--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jyoth\Downloads\Test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC0CE6B5-5082-4856-BD49-AAF483862355}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{338CC351-8099-4776-AB58-D36AAA5E825D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jyoth\Downloads\Test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{338CC351-8099-4776-AB58-D36AAA5E825D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0457C480-9669-4C1A-8730-D13E514E55D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -121,9 +121,6 @@
     <t>githubUsername</t>
   </si>
   <si>
-    <t>Jyothish9988</t>
-  </si>
-  <si>
     <t>githubShow</t>
   </si>
   <si>
@@ -628,9 +625,6 @@
     <t>GitHub</t>
   </si>
   <si>
-    <t>https://github.com/Jyothish9988</t>
-  </si>
-  <si>
     <t>n8n Creator</t>
   </si>
   <si>
@@ -650,6 +644,12 @@
   </si>
   <si>
     <t>AI Workflow Framework</t>
+  </si>
+  <si>
+    <t>https://github.com/jyothish-sl</t>
+  </si>
+  <si>
+    <t>jyothish-sl</t>
   </si>
 </sst>
 </file>
@@ -1083,36 +1083,36 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>167</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>182</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>183</v>
       </c>
       <c r="C3" s="4"/>
       <c r="D3" s="4"/>
@@ -1135,30 +1135,30 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="C1" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>84</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>184</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="C2" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="D2" s="4" t="s">
         <v>186</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>187</v>
       </c>
     </row>
   </sheetData>
@@ -1177,26 +1177,26 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>82</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>188</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>190</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>191</v>
       </c>
     </row>
   </sheetData>
@@ -1215,50 +1215,50 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>193</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>195</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
   </sheetData>
@@ -1328,7 +1328,7 @@
         <v>21</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
@@ -1360,12 +1360,12 @@
         <v>28</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>29</v>
+        <v>205</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B12" s="4">
         <v>6</v>
@@ -1390,31 +1390,31 @@
         <v>10</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>33</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>35</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -1433,186 +1433,186 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>37</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>39</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B10" s="4" t="s">
         <v>48</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B13" s="4" t="s">
         <v>51</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B17" s="4" t="s">
         <v>56</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B21" s="4" t="s">
         <v>60</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -1634,70 +1634,70 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="C1" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>67</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="C2" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="D2" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="E2" s="4" t="s">
         <v>72</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>70</v>
-      </c>
       <c r="C3" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D3" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="E3" s="4" t="s">
         <v>75</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="C4" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="D4" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="E4" s="4" t="s">
         <v>80</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -1719,93 +1719,93 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>84</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="C2" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="D2" s="4" t="s">
         <v>88</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>89</v>
       </c>
       <c r="E2" s="4"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="C3" s="4" t="s">
+      <c r="D3" s="4" t="s">
         <v>91</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>92</v>
       </c>
       <c r="E3" s="4"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="C4" s="4" t="s">
+      <c r="D4" s="4" t="s">
         <v>94</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>95</v>
       </c>
       <c r="E4" s="4"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="B5" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="C5" s="4" t="s">
+      <c r="D5" s="4" t="s">
         <v>97</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>98</v>
       </c>
       <c r="E5" s="4"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="C6" s="4" t="s">
+      <c r="D6" s="4" t="s">
         <v>100</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>101</v>
       </c>
       <c r="E6" s="4"/>
     </row>
@@ -1832,157 +1832,157 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="D1" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="I1" s="3" t="s">
-        <v>108</v>
-      </c>
       <c r="J1" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="B2" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="C2" s="4" t="s">
+      <c r="D2" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="E2" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="F2" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="G2" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="H2" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="I2" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="I2" s="4" t="s">
-        <v>116</v>
-      </c>
       <c r="J2" s="4" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="C3" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="D3" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="D3" s="4" t="s">
+      <c r="E3" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="F3" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="G3" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="H3" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="I3" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="I3" s="4" t="s">
-        <v>125</v>
-      </c>
       <c r="J3" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="C4" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="D4" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="E4" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="E4" s="4" t="s">
+      <c r="F4" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="G4" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="H4" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="I4" s="4" t="s">
         <v>132</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>133</v>
       </c>
       <c r="J4" s="4"/>
     </row>
     <row r="5" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="C5" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="E5" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="C5" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="E5" s="4" t="s">
+      <c r="F5" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="G5" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="H5" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="I5" s="4" t="s">
         <v>139</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>140</v>
       </c>
       <c r="J5" s="4"/>
     </row>
@@ -2003,145 +2003,145 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="C1" s="3" t="s">
         <v>142</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B2" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>144</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B3" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>146</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B4" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>148</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B5" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>150</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B6" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>152</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B7" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="C7" s="4" t="s">
         <v>154</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B8" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="C8" s="4" t="s">
         <v>156</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B9" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="C9" s="4" t="s">
         <v>158</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B10" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="C10" s="4" t="s">
         <v>160</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B12" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="C12" s="4" t="s">
         <v>163</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B13" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="C13" s="4" t="s">
         <v>165</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>166</v>
       </c>
     </row>
   </sheetData>
@@ -2162,84 +2162,84 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>167</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>169</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>170</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="4"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C3" s="4"/>
       <c r="D3" s="4"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>172</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>173</v>
       </c>
       <c r="C4" s="4"/>
       <c r="D4" s="4"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>176</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>177</v>
       </c>
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="B8" s="4" t="s">
         <v>178</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>179</v>
       </c>
       <c r="C8" s="4"/>
       <c r="D8" s="4"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jyoth\Downloads\Test\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER1\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0457C480-9669-4C1A-8730-D13E514E55D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="12460" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -32,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="224">
   <si>
     <t>HOW THIS FILE WORKS</t>
   </si>
@@ -364,21 +363,6 @@
     <t>2026</t>
   </si>
   <si>
-    <t>Full-stack</t>
-  </si>
-  <si>
-    <t>A self-built platform for creating and running AI workflows, with a Next.js frontend and FastAPI backend.</t>
-  </si>
-  <si>
-    <t>Describe the problem this project solves and who it is for. | Describe your role, what you designed, and one decision you are proud of.</t>
-  </si>
-  <si>
-    <t>Next.js 15 web app | FastAPI REST backend | PostgreSQL data layer | Docker setup for local and server deployment</t>
-  </si>
-  <si>
-    <t>Next.js 15, FastAPI, PostgreSQL, Docker</t>
-  </si>
-  <si>
     <t>projects/ai-workflow-saas/cover.png</t>
   </si>
   <si>
@@ -394,18 +378,6 @@
     <t>AI</t>
   </si>
   <si>
-    <t>Full-stack app that classifies incoming emails with a LangGraph agent and routes them by confidence.</t>
-  </si>
-  <si>
-    <t>Describe how emails flow through the system and what happens at each step. | Describe how low-confidence emails are handled.</t>
-  </si>
-  <si>
-    <t>LangGraph email classification | Confidence-based auto-routing | React and Vite dashboard | FastAPI backend with PostgreSQL, Redis and Celery for background jobs</t>
-  </si>
-  <si>
-    <t>FastAPI, React, Vite, LangGraph, PostgreSQL, Redis, Celery</t>
-  </si>
-  <si>
     <t>projects/email-agent/cover.png</t>
   </si>
   <si>
@@ -650,12 +622,93 @@
   </si>
   <si>
     <t>jyothish-sl</t>
+  </si>
+  <si>
+    <t>Full-stack AI Automation</t>
+  </si>
+  <si>
+    <t>A full-stack email automation platform that connects mailbox fetching, AI-powered email classification, configurable automation agents, scheduled execution, and LLM usage monitoring through a web dashboard.</t>
+  </si>
+  <si>
+    <t>Designed and developed a full-stack email automation application with a React frontend and asynchronous FastAPI backend. The platform manages email credentials, fetches and stores incoming messages, supports configurable classification rules, and schedules automation agents. A key architectural decision was to separate mailbox access, agent execution, API routes, and database models into distinct modules, making the application easier to extend and maintain.</t>
+  </si>
+  <si>
+    <t>User registration and authentication | mailbox credential management | IMAP-based email fetching | duplicate-message filtering | configurable email classification | AI agent execution using LangGraph | scheduled automation | email search and status filters | dashboard activity and statistics | LLM token-usage charts | PostgreSQL persistence | Docker Compose deployment.</t>
+  </si>
+  <si>
+    <t>Python, FastAPI, React 19, Vite, PostgreSQL 16, SQLAlchemy 2, LangGraph, LangChain, OpenAI, Anthropic, Ollama, APScheduler, Docker, Docker Compose, Recharts</t>
+  </si>
+  <si>
+    <t>A self-hosted AI workflow automation platform for building, executing, scheduling, and monitoring visual workflows with LLM-powered automation and external application integrations.</t>
+  </si>
+  <si>
+    <t>Designed and developed a full-stack AI workflow automation platform that combines a visual workflow builder with a FastAPI execution engine. The platform supports configurable LLM providers, conditional branching, loops, scheduled execution, workflow history, and integrations with external applications. A key design decision was to separate workflow definitions from backend execution handlers, making the system extensible without redesigning the core engine.</t>
+  </si>
+  <si>
+    <t>Visual workflow builder | node-based execution engine | AI Agent with OpenAI, Anthropic, Groq, and Ollama support | conditional branching and loops | cron-based scheduling | Gmail automation | Slack, Discord, and Telegram integrations | encrypted integration credentials | JWT authentication | execution history and logging | Docker-based deployment.</t>
+  </si>
+  <si>
+    <t>React 18, Vite, React Flow, Python 3.11, FastAPI, PostgreSQL, SQLAlchemy, OpenAI API, Anthropic API, Groq, Ollama, Docker, Docker Compose, Nginx</t>
+  </si>
+  <si>
+    <t>rss-linkedin-automation</t>
+  </si>
+  <si>
+    <t>RSS-to-LinkedIn AI Automation</t>
+  </si>
+  <si>
+    <t>AI Automation &amp; Workflow Integration</t>
+  </si>
+  <si>
+    <t>An AI-powered content automation workflow that transforms RSS news articles into structured, summarized LinkedIn posts using Ollama, PostgreSQL, n8n, and Telegram-based human approval.</t>
+  </si>
+  <si>
+    <t>Designed and developed an automated content publishing workflow using n8n to fetch RSS articles, generate AI-powered summaries, extract metadata, and classify content using a locally hosted Ollama model. The workflow stores processed articles and their approval status in PostgreSQL, while Telegram enables human review through approval and rejection actions. Approved content proceeds to LinkedIn publishing, ensuring controlled, efficient, and brand-conscious content automation.</t>
+  </si>
+  <si>
+    <t>RSS feed integration and article fetching | AI-powered article summarization | Metadata extraction and content classification | Keyword and sentiment analysis | Key-point generation | Ollama local LLM integration | PostgreSQL persistence | Human-in-the-loop approval using Telegram | Approval and rejection handling | Automated LinkedIn publishing | Article status tracking | Structured content storage.</t>
+  </si>
+  <si>
+    <t>n8n, Ollama, PostgreSQL, Telegram Bot API, LinkedIn API, RSS Feeds, OAuth 2.0, Python (optional supporting utilities), Qwen 2.5 3B (or another compatible Ollama model)</t>
+  </si>
+  <si>
+    <t>Code=https://n8n.io/workflows/15720-publish-linkedin-posts-from-rss-using-ollama-postgresql-and-telegram-approval/</t>
+  </si>
+  <si>
+    <t>projects/rss-linkedin-automation/cover.png</t>
+  </si>
+  <si>
+    <t>gmail-ai-support-tickets</t>
+  </si>
+  <si>
+    <t>AI-Powered Gmail Support Ticket Automation</t>
+  </si>
+  <si>
+    <t>AI Automation &amp; Ticket Management</t>
+  </si>
+  <si>
+    <t>An AI-powered support automation workflow that converts incoming Gmail messages into categorized support tickets, generates unique ticket IDs, stores records in PostgreSQL, assigns support agents based on workload, and sends automated email confirmations.</t>
+  </si>
+  <si>
+    <t>Designed and developed an intelligent customer support workflow using n8n to automate ticket creation and assignment. The workflow retrieves incoming Gmail messages, uses Ollama or a compatible large language model to classify issues such as payment problems, login errors, and fraud alerts, and generates unique ticket identifiers. Structured ticket data is stored in PostgreSQL, with support agent assignments and assignment history tracked in dedicated database tables. The system selects available support agents based on workload and sends automated email confirmations to customers, improving response efficiency, consistency, and ticket traceability.</t>
+  </si>
+  <si>
+    <t>Gmail integration and email fetching | AI-powered ticket classification | Payment, login, fraud, and technical issue categorization | Automatic ticket ID generation | PostgreSQL ticket storage | Workload-based support agent assignment | Support assignment history logging | Automated customer email confirmations | Ticket status tracking | Structured support data management | LLM integration using Ollama | Workflow automation with n8n.</t>
+  </si>
+  <si>
+    <t>n8n, Gmail API, Gmail OAuth2, Ollama, Large Language Models (LLMs), PostgreSQL, SQL, AI Classification, Workflow Automation, Email Automation</t>
+  </si>
+  <si>
+    <t>projects/gmail-ai-support-tickets/cover.png</t>
+  </si>
+  <si>
+    <t>Code=https://n8n.io/workflows/15522-classify-gmail-support-emails-with-ai-and-store-tickets-in-postgresql/</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -701,7 +754,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -712,6 +765,9 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1014,54 +1070,54 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:A9"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="130" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="17.399999999999999" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:1" ht="17" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>8</v>
       </c>
@@ -1072,47 +1128,47 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="34" customWidth="1"/>
     <col min="3" max="3" width="30" customWidth="1"/>
     <col min="4" max="4" width="44" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>81</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>32</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="4" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C3" s="4"/>
       <c r="D3" s="4"/>
@@ -1123,9 +1179,9 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
     <col min="2" max="2" width="80" customWidth="1"/>
@@ -1133,7 +1189,7 @@
     <col min="4" max="4" width="50" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>81</v>
       </c>
@@ -1147,18 +1203,18 @@
         <v>84</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
     </row>
   </sheetData>
@@ -1167,15 +1223,15 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
     <col min="2" max="2" width="90" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>81</v>
       </c>
@@ -1183,20 +1239,20 @@
         <v>82</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
     </row>
   </sheetData>
@@ -1205,60 +1261,60 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>30</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="B3" s="4" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="4" t="s">
-        <v>196</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
     </row>
   </sheetData>
@@ -1267,15 +1323,15 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B12"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="110" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>9</v>
       </c>
@@ -1283,7 +1339,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
         <v>11</v>
       </c>
@@ -1291,7 +1347,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
         <v>13</v>
       </c>
@@ -1299,7 +1355,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
         <v>15</v>
       </c>
@@ -1307,7 +1363,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
         <v>17</v>
       </c>
@@ -1315,7 +1371,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
         <v>19</v>
       </c>
@@ -1323,15 +1379,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
         <v>21</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
         <v>22</v>
       </c>
@@ -1339,7 +1395,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
         <v>24</v>
       </c>
@@ -1347,7 +1403,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
         <v>26</v>
       </c>
@@ -1355,15 +1411,15 @@
         <v>27</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="s">
         <v>28</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" s="4" t="s">
         <v>29</v>
       </c>
@@ -1377,15 +1433,15 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>10</v>
       </c>
@@ -1393,15 +1449,15 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
         <v>31</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
         <v>32</v>
       </c>
@@ -1409,7 +1465,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
         <v>34</v>
       </c>
@@ -1423,15 +1479,15 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B23"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="2" width="32" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>36</v>
       </c>
@@ -1439,7 +1495,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
         <v>38</v>
       </c>
@@ -1447,7 +1503,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
         <v>38</v>
       </c>
@@ -1455,7 +1511,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
         <v>38</v>
       </c>
@@ -1463,7 +1519,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
         <v>38</v>
       </c>
@@ -1471,7 +1527,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
         <v>38</v>
       </c>
@@ -1479,7 +1535,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
         <v>38</v>
       </c>
@@ -1487,7 +1543,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
         <v>38</v>
       </c>
@@ -1495,7 +1551,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
         <v>38</v>
       </c>
@@ -1503,7 +1559,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
         <v>47</v>
       </c>
@@ -1511,7 +1567,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="s">
         <v>47</v>
       </c>
@@ -1519,7 +1575,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" s="4" t="s">
         <v>47</v>
       </c>
@@ -1527,7 +1583,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" s="4" t="s">
         <v>50</v>
       </c>
@@ -1535,7 +1591,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" s="4" t="s">
         <v>50</v>
       </c>
@@ -1543,7 +1599,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="s">
         <v>50</v>
       </c>
@@ -1551,7 +1607,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" s="4" t="s">
         <v>50</v>
       </c>
@@ -1559,7 +1615,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" s="4" t="s">
         <v>55</v>
       </c>
@@ -1567,7 +1623,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" s="4" t="s">
         <v>55</v>
       </c>
@@ -1575,7 +1631,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" s="4" t="s">
         <v>55</v>
       </c>
@@ -1583,7 +1639,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" s="4" t="s">
         <v>59</v>
       </c>
@@ -1591,7 +1647,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" s="4" t="s">
         <v>59</v>
       </c>
@@ -1599,7 +1655,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" s="4" t="s">
         <v>59</v>
       </c>
@@ -1607,7 +1663,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" s="4" t="s">
         <v>59</v>
       </c>
@@ -1621,9 +1677,9 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
     <col min="2" max="2" width="26" customWidth="1"/>
@@ -1632,7 +1688,7 @@
     <col min="5" max="5" width="100" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>63</v>
       </c>
@@ -1649,7 +1705,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
         <v>68</v>
       </c>
@@ -1666,7 +1722,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" ht="87" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
         <v>68</v>
       </c>
@@ -1683,7 +1739,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
         <v>76</v>
       </c>
@@ -1706,9 +1762,9 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -1717,7 +1773,7 @@
     <col min="5" max="5" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>81</v>
       </c>
@@ -1734,7 +1790,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
         <v>85</v>
       </c>
@@ -1749,7 +1805,7 @@
       </c>
       <c r="E2" s="4"/>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
         <v>89</v>
       </c>
@@ -1764,7 +1820,7 @@
       </c>
       <c r="E3" s="4"/>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
         <v>92</v>
       </c>
@@ -1779,7 +1835,7 @@
       </c>
       <c r="E4" s="4"/>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
         <v>95</v>
       </c>
@@ -1794,7 +1850,7 @@
       </c>
       <c r="E5" s="4"/>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
         <v>98</v>
       </c>
@@ -1815,9 +1871,9 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:J5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:J7"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
@@ -1830,7 +1886,7 @@
     <col min="10" max="10" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>101</v>
       </c>
@@ -1862,129 +1918,193 @@
         <v>84</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" ht="87" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
         <v>108</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="I2" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="E2" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="F2" s="4" t="s">
+      <c r="J2" s="4" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="101.5" x14ac:dyDescent="0.35">
+      <c r="A3" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="B3" s="4" t="s">
         <v>113</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A3" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>118</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="101.5" x14ac:dyDescent="0.35">
+      <c r="A4" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="C4" s="4">
+        <v>2026</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="130.5" x14ac:dyDescent="0.35">
+      <c r="A5" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="C5" s="4">
+        <v>2026</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+      <c r="A6" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="E6" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="F6" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="G6" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="H6" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="I6" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="J6" s="4"/>
+    </row>
+    <row r="7" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+      <c r="A7" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="J3" s="4" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A4" s="4" t="s">
+      <c r="B7" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="C7" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="E7" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="F7" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="E4" s="4" t="s">
+      <c r="G7" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="H7" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="I7" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="H4" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="J4" s="4"/>
-    </row>
-    <row r="5" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A5" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="J5" s="4"/>
+      <c r="J7" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1992,156 +2112,156 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="2" width="44" customWidth="1"/>
     <col min="3" max="3" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
         <v>108</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
         <v>108</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
         <v>108</v>
       </c>
       <c r="B4" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="C8" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="C4" s="4" t="s">
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="B9" s="4" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="B5" s="4" t="s">
+      <c r="C9" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="C5" s="4" t="s">
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A10" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="B10" s="4" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="B6" s="4" t="s">
+      <c r="C10" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="C6" s="4" t="s">
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A11" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="B11" s="4" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="B7" s="4" t="s">
+      <c r="C11" s="4" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A12" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="B12" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C12" s="4" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="B8" s="4" t="s">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A13" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="B13" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C13" s="4" t="s">
         <v>156</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>165</v>
       </c>
     </row>
   </sheetData>
@@ -2150,9 +2270,9 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D8"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="44" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
@@ -2160,86 +2280,86 @@
     <col min="4" max="4" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>81</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="4"/>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="C3" s="4"/>
       <c r="D3" s="4"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="C4" s="4"/>
       <c r="D4" s="4"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>176</v>
+        <v>167</v>
       </c>
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
       <c r="C8" s="4"/>
       <c r="D8" s="4"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="12460" activeTab="6"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="12460" firstSheet="4" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -471,15 +471,6 @@
     <t>Routing rules</t>
   </si>
   <si>
-    <t>projects/rag-knowledge-base/1.png</t>
-  </si>
-  <si>
-    <t>Upload flow</t>
-  </si>
-  <si>
-    <t>projects/rag-knowledge-base/2.png</t>
-  </si>
-  <si>
     <t>n8n workflow</t>
   </si>
   <si>
@@ -703,6 +694,15 @@
   </si>
   <si>
     <t>Code=https://n8n.io/workflows/15522-classify-gmail-support-emails-with-ai-and-store-tickets-in-postgresql/</t>
+  </si>
+  <si>
+    <t>projects/rss-linkedin-automation/1.png</t>
+  </si>
+  <si>
+    <t>projects/gmail-ai-support-tickets/1.png</t>
+  </si>
+  <si>
+    <t>Cover</t>
   </si>
 </sst>
 </file>
@@ -1142,33 +1142,33 @@
         <v>81</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>132</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>32</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="4" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="C3" s="4"/>
       <c r="D3" s="4"/>
@@ -1205,16 +1205,16 @@
     </row>
     <row r="2" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>174</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>177</v>
       </c>
     </row>
   </sheetData>
@@ -1241,18 +1241,18 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
   </sheetData>
@@ -1274,47 +1274,47 @@
         <v>30</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
     </row>
   </sheetData>
@@ -1384,7 +1384,7 @@
         <v>21</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
@@ -1416,7 +1416,7 @@
         <v>28</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
@@ -1454,7 +1454,7 @@
         <v>31</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
@@ -1923,31 +1923,31 @@
         <v>108</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>109</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="E2" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="H2" s="4" t="s">
         <v>202</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>203</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>204</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>205</v>
       </c>
       <c r="I2" s="4" t="s">
         <v>110</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="101.5" x14ac:dyDescent="0.35">
@@ -1961,19 +1961,19 @@
         <v>109</v>
       </c>
       <c r="D3" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="G3" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="H3" s="4" t="s">
         <v>198</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>201</v>
       </c>
       <c r="I3" s="4" t="s">
         <v>115</v>
@@ -1984,66 +1984,66 @@
     </row>
     <row r="4" spans="1:10" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="C4" s="4">
         <v>2026</v>
       </c>
       <c r="D4" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="G4" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="H4" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="I4" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="J4" s="4" t="s">
         <v>210</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>211</v>
-      </c>
-      <c r="H4" s="5" t="s">
-        <v>212</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>214</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A5" s="5" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="C5" s="4">
         <v>2026</v>
       </c>
       <c r="D5" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="G5" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="H5" s="5" t="s">
         <v>218</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="I5" s="5" t="s">
         <v>219</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="J5" s="5" t="s">
         <v>220</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>221</v>
-      </c>
-      <c r="I5" s="5" t="s">
-        <v>222</v>
-      </c>
-      <c r="J5" s="5" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="29" x14ac:dyDescent="0.35">
@@ -2199,25 +2199,25 @@
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A8" s="4" t="s">
-        <v>116</v>
+      <c r="A8" s="5" t="s">
+        <v>203</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>146</v>
+        <v>221</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>147</v>
+        <v>223</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A9" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>148</v>
+      <c r="A9" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>222</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>149</v>
+        <v>223</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
@@ -2225,10 +2225,10 @@
         <v>116</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
@@ -2236,10 +2236,10 @@
         <v>124</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
@@ -2247,10 +2247,10 @@
         <v>124</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
@@ -2258,10 +2258,10 @@
         <v>124</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
     </row>
   </sheetData>
@@ -2285,81 +2285,81 @@
         <v>81</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>132</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="4"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C3" s="4"/>
       <c r="D3" s="4"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C4" s="4"/>
       <c r="D4" s="4"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C8" s="4"/>
       <c r="D8" s="4"/>
